--- a/Input/urbs_intertemporal_2050/2026.xlsx
+++ b/Input/urbs_intertemporal_2050/2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxoi\GitHub\urbs-extension\Input\urbs_intertemporal_2050\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BF6B9C-CD77-491C-9343-D01C4140044A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5224B635-0826-4DE2-B25D-3FB3EDFBA4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-1935" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global" sheetId="1" r:id="rId1"/>
@@ -2336,8 +2336,9 @@
       <c r="D29" s="19">
         <v>1</v>
       </c>
-      <c r="E29" s="19">
-        <v>1.2</v>
+      <c r="E29" s="19" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -2371,18 +2372,18 @@
       <c r="D31" s="19">
         <v>0.20499999999999999</v>
       </c>
-      <c r="E31" s="19">
-        <f>D31*E29</f>
-        <v>0.24599999999999997</v>
+      <c r="E31" s="19" t="e">
+        <f>NA()</f>
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A30:C31 E30:E31">
+  <conditionalFormatting sqref="A30:C31">
     <cfRule type="expression" dxfId="4" priority="10">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A20:E25 A26 C26:D26 A29:E29 A27:D28">
+  <conditionalFormatting sqref="A20:E25 A26 C26:D26 A27:D29">
     <cfRule type="expression" dxfId="3" priority="5">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
@@ -2434,7 +2435,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D29:E29 E30:E31">
+  <conditionalFormatting sqref="D29">
     <cfRule type="dataBar" priority="8">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2452,8 +2453,6 @@
     <cfRule type="expression" dxfId="1" priority="3">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E7">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2467,12 +2466,10 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E26:E28">
+  <conditionalFormatting sqref="E26:E31">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>NOT(EXACT(INDIRECT("Z"&amp;ROW()-1&amp;"S1",FALSE()), INDIRECT("Z"&amp;ROW()&amp;"S1",FALSE())))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E26:E28">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2533,7 +2530,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D29:E29 E30:E31</xm:sqref>
+          <xm:sqref>D29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{C94904AD-7F56-4C00-BC40-E02F3258F971}">
@@ -2563,7 +2560,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E26:E28</xm:sqref>
+          <xm:sqref>E26:E31</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
